--- a/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,64; 30,33</t>
+          <t>18,5; 30,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,99; 65,85</t>
+          <t>52,32; 65,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,45; 53,81</t>
+          <t>38,6; 52,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 13,88</t>
+          <t>6,46; 14,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,37; 43,53</t>
+          <t>29,88; 44,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,27; 65,5</t>
+          <t>53,02; 65,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,03; 57,18</t>
+          <t>44,18; 57,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 15,77</t>
+          <t>9,53; 16,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,5; 35,02</t>
+          <t>25,8; 34,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,54; 63,81</t>
+          <t>54,95; 63,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,52; 52,98</t>
+          <t>43,66; 53,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 13,8</t>
+          <t>8,89; 13,71</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,87; 23,47</t>
+          <t>15,12; 23,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,74; 53,74</t>
+          <t>42,96; 53,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,41; 23,97</t>
+          <t>15,83; 23,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15,63; 25,97</t>
+          <t>16,05; 25,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,38; 28,23</t>
+          <t>20,23; 28,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,37; 58,03</t>
+          <t>48,34; 57,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,75; 28,02</t>
+          <t>19,6; 27,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,45; 31,24</t>
+          <t>23,65; 31,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,08; 24,81</t>
+          <t>19,11; 24,66</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,18; 54,3</t>
+          <t>47,3; 54,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,29; 24,69</t>
+          <t>18,72; 24,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,51; 27,66</t>
+          <t>21,33; 27,52</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 24,41</t>
+          <t>14,41; 24,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,23; 54,4</t>
+          <t>42,28; 54,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,7; 30,17</t>
+          <t>20,12; 30,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,68; 23,99</t>
+          <t>14,9; 24,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,48; 37,43</t>
+          <t>26,14; 37,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,05; 60,66</t>
+          <t>48,83; 60,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,9; 35,89</t>
+          <t>25,36; 36,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,25; 28,06</t>
+          <t>19,54; 27,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,0; 29,45</t>
+          <t>22,25; 29,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,48; 55,96</t>
+          <t>47,18; 56,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,17; 31,94</t>
+          <t>24,06; 32,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>18,08; 24,72</t>
+          <t>17,95; 24,32</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,46; 19,03</t>
+          <t>10,5; 19,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,79; 63,96</t>
+          <t>51,46; 63,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,72; 47,05</t>
+          <t>34,86; 46,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,32; 35,26</t>
+          <t>21,4; 35,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,59; 27,86</t>
+          <t>18,94; 27,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,37; 67,73</t>
+          <t>56,32; 67,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,09; 52,91</t>
+          <t>41,31; 52,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,14; 26,52</t>
+          <t>10,44; 26,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,37; 22,64</t>
+          <t>16,23; 22,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,45; 64,02</t>
+          <t>56,58; 64,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40,34; 48,85</t>
+          <t>39,86; 48,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,14; 27,82</t>
+          <t>14,12; 27,48</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,99; 35,23</t>
+          <t>20,05; 34,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,71; 61,42</t>
+          <t>45,71; 61,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,03; 66,82</t>
+          <t>52,58; 66,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,65; 30,88</t>
+          <t>16,79; 31,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,67; 30,87</t>
+          <t>17,53; 30,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,89; 61,92</t>
+          <t>48,39; 62,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,83; 71,12</t>
+          <t>57,82; 71,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 23,61</t>
+          <t>7,52; 24,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,4; 30,81</t>
+          <t>21,19; 30,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,63; 59,44</t>
+          <t>49,0; 59,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56,81; 67,06</t>
+          <t>57,16; 67,23</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,85; 23,94</t>
+          <t>10,68; 24,23</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 20,81</t>
+          <t>10,71; 20,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,45; 59,5</t>
+          <t>45,42; 59,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,96; 50,16</t>
+          <t>35,7; 49,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,02; 34,16</t>
+          <t>22,99; 34,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,52; 26,47</t>
+          <t>16,01; 26,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,13; 53,56</t>
+          <t>41,6; 53,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,76; 51,76</t>
+          <t>38,13; 52,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,36; 38,91</t>
+          <t>29,48; 39,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,74; 21,76</t>
+          <t>14,69; 21,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45,17; 54,29</t>
+          <t>45,2; 54,21</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38,28; 48,17</t>
+          <t>39,07; 48,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,81; 35,01</t>
+          <t>27,62; 35,08</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,56; 23,9</t>
+          <t>16,28; 23,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,16; 53,01</t>
+          <t>43,47; 52,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,62; 40,89</t>
+          <t>31,09; 40,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,54</t>
+          <t>8,62; 15,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,24; 29,77</t>
+          <t>22,55; 29,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,66; 52,22</t>
+          <t>43,69; 52,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,94; 48,97</t>
+          <t>40,12; 49,02</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,29; 72,7</t>
+          <t>12,53; 73,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,64; 26,12</t>
+          <t>20,75; 26,43</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44,91; 50,66</t>
+          <t>45,1; 51,22</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37,64; 44,07</t>
+          <t>37,53; 44,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,06; 63,88</t>
+          <t>12,0; 62,24</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,39; 34,21</t>
+          <t>26,17; 34,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47,8; 56,38</t>
+          <t>48,22; 56,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56,51; 64,31</t>
+          <t>56,0; 64,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,09; 44,24</t>
+          <t>35,91; 44,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,71; 29,72</t>
+          <t>22,59; 29,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,97; 59,67</t>
+          <t>51,94; 59,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,41; 68,96</t>
+          <t>60,92; 68,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,42; 51,03</t>
+          <t>43,79; 50,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,33; 30,47</t>
+          <t>25,61; 30,63</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51,42; 57,04</t>
+          <t>51,58; 57,35</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60,11; 65,69</t>
+          <t>59,87; 65,76</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>40,88; 46,55</t>
+          <t>41,16; 46,71</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,24; 23,52</t>
+          <t>20,23; 23,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49,81; 53,79</t>
+          <t>49,74; 53,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,52; 43,46</t>
+          <t>39,73; 43,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21,13; 24,95</t>
+          <t>21,06; 24,74</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,72; 27,85</t>
+          <t>24,54; 27,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,36; 55,89</t>
+          <t>52,24; 55,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,1; 48,91</t>
+          <t>45,12; 48,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25,01; 46,79</t>
+          <t>25,08; 47,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23,03; 25,45</t>
+          <t>23,06; 25,44</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51,69; 54,52</t>
+          <t>51,7; 54,44</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43,1; 45,9</t>
+          <t>43,2; 45,9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,99; 38,28</t>
+          <t>23,9; 38,44</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35743; 58164</t>
+          <t>35473; 58817</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>122319; 154912</t>
+          <t>123083; 153746</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89673; 122316</t>
+          <t>87748; 119565</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17175; 34884</t>
+          <t>16231; 35548</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56459; 86632</t>
+          <t>59467; 87988</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>141055; 176748</t>
+          <t>143060; 177266</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>110243; 143174</t>
+          <t>110621; 142772</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23493; 39611</t>
+          <t>23933; 40874</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>99658; 136860</t>
+          <t>100820; 136384</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>275467; 322295</t>
+          <t>277556; 322351</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>207906; 253115</t>
+          <t>208579; 254504</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44176; 69321</t>
+          <t>44687; 68884</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55619; 87751</t>
+          <t>56557; 87078</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>170105; 213880</t>
+          <t>170982; 212326</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59055; 91859</t>
+          <t>60643; 91485</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>52867; 87861</t>
+          <t>54295; 87486</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90668; 125596</t>
+          <t>89997; 125343</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>223069; 267637</t>
+          <t>222969; 266864</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88532; 125643</t>
+          <t>87888; 123334</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>97225; 129549</t>
+          <t>98065; 131415</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>156264; 203186</t>
+          <t>156490; 201932</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>405403; 466563</t>
+          <t>406381; 464829</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>160386; 205320</t>
+          <t>155688; 203634</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>161925; 208261</t>
+          <t>160616; 207173</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>33276; 58719</t>
+          <t>34674; 58770</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>112054; 144363</t>
+          <t>112182; 144947</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46478; 71181</t>
+          <t>47473; 71938</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33318; 54472</t>
+          <t>33831; 55433</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>75728; 107034</t>
+          <t>74758; 105872</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>145762; 180273</t>
+          <t>145123; 180432</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66948; 96496</t>
+          <t>68179; 97357</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51328; 74823</t>
+          <t>52115; 73575</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>115833; 155093</t>
+          <t>117190; 155546</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>267071; 314783</t>
+          <t>265413; 316109</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122010; 161236</t>
+          <t>121461; 162404</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89266; 122026</t>
+          <t>88606; 120077</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27901; 50762</t>
+          <t>27993; 51467</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>162729; 200998</t>
+          <t>161717; 199949</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94377; 127916</t>
+          <t>94756; 126422</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>44942; 74316</t>
+          <t>45101; 74258</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>59805; 89631</t>
+          <t>60920; 89816</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>201921; 238362</t>
+          <t>198212; 238385</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>143376; 180231</t>
+          <t>140709; 179310</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>43539; 103678</t>
+          <t>40801; 105358</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96345; 133196</t>
+          <t>95502; 132639</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>376084; 426511</t>
+          <t>376949; 426759</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>247063; 299229</t>
+          <t>244170; 295131</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>91095; 167363</t>
+          <t>84956; 165343</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31866; 53469</t>
+          <t>30437; 52006</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>80240; 107831</t>
+          <t>80244; 107448</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>89835; 115364</t>
+          <t>90781; 114925</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16057; 29779</t>
+          <t>16187; 30471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34939; 57785</t>
+          <t>32805; 57468</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>97247; 125748</t>
+          <t>98255; 126016</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>107700; 132436</t>
+          <t>107675; 133578</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13483; 44580</t>
+          <t>14205; 45687</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>72520; 104419</t>
+          <t>71824; 104050</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>184110; 225062</t>
+          <t>185513; 224796</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>203876; 240674</t>
+          <t>205119; 241267</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30941; 68305</t>
+          <t>30474; 69126</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22952; 44572</t>
+          <t>22952; 43792</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>107000; 137052</t>
+          <t>104617; 136661</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69713; 97232</t>
+          <t>69202; 95112</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46867; 69542</t>
+          <t>46812; 69323</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37408; 59952</t>
+          <t>36259; 60656</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>105071; 136833</t>
+          <t>106287; 136967</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>79566; 109066</t>
+          <t>80347; 110412</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>61025; 80880</t>
+          <t>61288; 82190</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64941; 95910</t>
+          <t>64755; 96435</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>219456; 263776</t>
+          <t>219574; 263354</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>154863; 194888</t>
+          <t>158058; 196193</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>114451; 144068</t>
+          <t>113642; 144340</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>73017; 105414</t>
+          <t>71789; 105352</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>226077; 277676</t>
+          <t>227721; 275372</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>134153; 179116</t>
+          <t>136207; 178958</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35171; 64012</t>
+          <t>35503; 65774</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>119754; 160311</t>
+          <t>121428; 159561</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>263575; 315238</t>
+          <t>263708; 314327</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>221318; 271313</t>
+          <t>222283; 271583</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>82912; 490499</t>
+          <t>84561; 493758</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>202169; 255882</t>
+          <t>203307; 258871</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>506342; 571162</t>
+          <t>508508; 577535</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>373461; 437256</t>
+          <t>372323; 437270</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>131054; 694171</t>
+          <t>130415; 676363</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>154255; 199917</t>
+          <t>152931; 199317</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>289522; 341509</t>
+          <t>292053; 342547</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>325557; 370491</t>
+          <t>322634; 370107</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>150836; 190175</t>
+          <t>154359; 191356</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>152034; 199006</t>
+          <t>151235; 197550</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>364422; 418428</t>
+          <t>364172; 420569</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>426095; 478516</t>
+          <t>422707; 477882</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>234017; 275031</t>
+          <t>236019; 274828</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>317622; 382156</t>
+          <t>321164; 384120</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>672019; 745423</t>
+          <t>674066; 749433</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>763343; 834205</t>
+          <t>760352; 835157</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>396110; 450983</t>
+          <t>398780; 452542</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>498707; 579750</t>
+          <t>498664; 585848</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1368979; 1478154</t>
+          <t>1366860; 1474978</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>987571; 1086042</t>
+          <t>992738; 1089928</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>458338; 541364</t>
+          <t>456947; 536612</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>710346; 800129</t>
+          <t>705160; 801015</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1645976; 1756874</t>
+          <t>1642075; 1759869</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1331846; 1444516</t>
+          <t>1332406; 1446870</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>733652; 1372674</t>
+          <t>735655; 1404661</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1229084; 1358587</t>
+          <t>1231143; 1358193</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3045590; 3212455</t>
+          <t>3046118; 3207681</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2350037; 2502291</t>
+          <t>2355148; 2502314</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1224278; 1953711</t>
+          <t>1219515; 1961677</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,5; 30,67</t>
+          <t>18,05; 30,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,32; 65,35</t>
+          <t>52,13; 65,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38,6; 52,6</t>
+          <t>39,96; 52,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,14</t>
+          <t>7,4; 14,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>29,88; 44,21</t>
+          <t>29,08; 43,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,02; 65,69</t>
+          <t>53,22; 66,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,18; 57,02</t>
+          <t>44,71; 57,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 16,28</t>
+          <t>9,96; 16,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,8; 34,9</t>
+          <t>25,82; 34,98</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54,95; 63,82</t>
+          <t>54,92; 63,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43,66; 53,27</t>
+          <t>43,37; 53,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,89; 13,71</t>
+          <t>9,43; 14,09</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,12; 23,29</t>
+          <t>14,96; 23,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,96; 53,35</t>
+          <t>43,02; 53,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,83; 23,87</t>
+          <t>15,84; 23,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,05; 25,86</t>
+          <t>17,05; 27,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,23; 28,17</t>
+          <t>20,4; 28,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,34; 57,86</t>
+          <t>48,1; 57,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,6; 27,51</t>
+          <t>19,83; 27,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,65; 31,69</t>
+          <t>24,37; 31,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19,11; 24,66</t>
+          <t>19,15; 24,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47,3; 54,1</t>
+          <t>46,9; 54,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18,72; 24,49</t>
+          <t>18,71; 24,91</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,33; 27,52</t>
+          <t>22,42; 28,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,41; 24,43</t>
+          <t>14,12; 24,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,28; 54,62</t>
+          <t>42,75; 54,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,12; 30,49</t>
+          <t>20,16; 30,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,9; 24,42</t>
+          <t>15,73; 25,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,14; 37,02</t>
+          <t>26,35; 36,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,83; 60,71</t>
+          <t>48,79; 60,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,36; 36,21</t>
+          <t>24,48; 35,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,54; 27,59</t>
+          <t>18,47; 26,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,25; 29,54</t>
+          <t>22,09; 29,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>47,18; 56,19</t>
+          <t>47,26; 55,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,06; 32,17</t>
+          <t>23,6; 31,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,95; 24,32</t>
+          <t>17,91; 23,97</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,5; 19,3</t>
+          <t>10,32; 18,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,46; 63,63</t>
+          <t>52,38; 63,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,86; 46,5</t>
+          <t>34,37; 46,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21,4; 35,24</t>
+          <t>22,4; 36,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,94; 27,92</t>
+          <t>19,24; 28,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,32; 67,73</t>
+          <t>57,06; 67,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,31; 52,64</t>
+          <t>41,19; 52,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,44; 26,95</t>
+          <t>22,15; 30,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,23; 22,54</t>
+          <t>16,02; 22,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56,58; 64,06</t>
+          <t>56,26; 64,28</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39,86; 48,18</t>
+          <t>39,81; 48,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,12; 27,48</t>
+          <t>23,31; 31,36</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,05; 34,26</t>
+          <t>20,32; 35,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,71; 61,2</t>
+          <t>44,98; 60,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,58; 66,57</t>
+          <t>52,08; 66,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,79; 31,6</t>
+          <t>17,7; 32,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,53; 30,7</t>
+          <t>18,2; 30,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,39; 62,06</t>
+          <t>48,27; 62,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,82; 71,73</t>
+          <t>57,86; 71,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 24,19</t>
+          <t>18,21; 28,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>21,19; 30,7</t>
+          <t>21,2; 30,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49,0; 59,37</t>
+          <t>49,27; 59,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>57,16; 67,23</t>
+          <t>57,07; 66,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,68; 24,23</t>
+          <t>19,53; 27,2</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10,71; 20,44</t>
+          <t>10,77; 20,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>45,42; 59,33</t>
+          <t>46,07; 59,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,7; 49,06</t>
+          <t>35,32; 49,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22,99; 34,05</t>
+          <t>24,97; 35,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,01; 26,78</t>
+          <t>16,2; 26,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,6; 53,61</t>
+          <t>41,43; 53,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,13; 52,4</t>
+          <t>37,46; 52,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,48; 39,54</t>
+          <t>28,98; 38,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,69; 21,88</t>
+          <t>14,71; 21,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45,2; 54,21</t>
+          <t>45,5; 54,56</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>39,07; 48,49</t>
+          <t>38,15; 48,28</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>27,62; 35,08</t>
+          <t>28,23; 35,54</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,28; 23,89</t>
+          <t>16,02; 24,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,47; 52,57</t>
+          <t>43,37; 52,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31,09; 40,85</t>
+          <t>31,41; 40,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 15,96</t>
+          <t>9,22; 15,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,55; 29,63</t>
+          <t>22,1; 29,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,69; 52,07</t>
+          <t>43,67; 51,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,12; 49,02</t>
+          <t>40,06; 48,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>12,53; 73,18</t>
+          <t>11,97; 17,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20,75; 26,43</t>
+          <t>20,87; 26,21</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,1; 51,22</t>
+          <t>44,63; 50,64</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37,53; 44,07</t>
+          <t>37,77; 44,38</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,0; 62,24</t>
+          <t>11,6; 15,63</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>43,94%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>26,17; 34,1</t>
+          <t>25,98; 33,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,22; 56,55</t>
+          <t>48,3; 56,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56,0; 64,24</t>
+          <t>56,05; 64,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35,91; 44,51</t>
+          <t>37,14; 46,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,59; 29,5</t>
+          <t>22,48; 29,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,94; 59,98</t>
+          <t>51,74; 59,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,92; 68,87</t>
+          <t>61,32; 69,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,79; 50,99</t>
+          <t>45,21; 52,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25,61; 30,63</t>
+          <t>25,34; 30,62</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51,58; 57,35</t>
+          <t>51,42; 57,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59,87; 65,76</t>
+          <t>60,08; 65,79</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>41,16; 46,71</t>
+          <t>42,57; 48,31</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,23; 23,77</t>
+          <t>20,06; 23,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49,74; 53,67</t>
+          <t>49,73; 53,75</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39,73; 43,61</t>
+          <t>39,59; 43,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21,06; 24,74</t>
+          <t>22,17; 25,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>24,54; 27,88</t>
+          <t>24,55; 27,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,24; 55,98</t>
+          <t>52,37; 55,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,12; 48,99</t>
+          <t>45,03; 48,71</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25,08; 47,88</t>
+          <t>26,41; 29,17</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23,06; 25,44</t>
+          <t>23,05; 25,45</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51,7; 54,44</t>
+          <t>51,58; 54,35</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43,2; 45,9</t>
+          <t>43,03; 45,77</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,9; 38,44</t>
+          <t>24,95; 27,22</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24929</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30907</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55837</t>
+          <t>60348</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>35473; 58817</t>
+          <t>34619; 58746</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>123083; 153746</t>
+          <t>122634; 154506</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87748; 119565</t>
+          <t>90846; 119752</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16231; 35548</t>
+          <t>18342; 35249</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59467; 87988</t>
+          <t>57865; 86224</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>143060; 177266</t>
+          <t>143599; 178104</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>110621; 142772</t>
+          <t>111964; 144359</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23933; 40874</t>
+          <t>26940; 43578</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100820; 136384</t>
+          <t>100906; 136691</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>277556; 322351</t>
+          <t>277379; 321143</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208579; 254504</t>
+          <t>207208; 253713</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44687; 68884</t>
+          <t>48893; 73044</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>69683</t>
+          <t>76819</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>112490</t>
+          <t>124692</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>182173</t>
+          <t>201511</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56557; 87078</t>
+          <t>55957; 86916</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>170982; 212326</t>
+          <t>171202; 212885</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60643; 91485</t>
+          <t>60688; 91837</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54295; 87486</t>
+          <t>59970; 96307</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89997; 125343</t>
+          <t>90766; 124686</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>222969; 266864</t>
+          <t>221836; 267048</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87888; 123334</t>
+          <t>88902; 125454</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>98065; 131415</t>
+          <t>107728; 140110</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>156490; 201932</t>
+          <t>156836; 204302</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>406381; 464829</t>
+          <t>402926; 467734</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>155688; 203634</t>
+          <t>155580; 207095</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>160616; 207173</t>
+          <t>177978; 225451</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43404</t>
+          <t>44544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61323</t>
+          <t>60902</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>104727</t>
+          <t>105447</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>34674; 58770</t>
+          <t>33970; 58214</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>112182; 144947</t>
+          <t>113433; 144568</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47473; 71938</t>
+          <t>47558; 72502</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33831; 55433</t>
+          <t>35798; 57558</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74758; 105872</t>
+          <t>75370; 105736</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>145123; 180432</t>
+          <t>144997; 180652</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>68179; 97357</t>
+          <t>65822; 96529</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>52115; 73575</t>
+          <t>50633; 72891</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>117190; 155546</t>
+          <t>116338; 155915</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>265413; 316109</t>
+          <t>265884; 314110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>121461; 162404</t>
+          <t>119111; 160027</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88606; 120077</t>
+          <t>89886; 120292</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>58802</t>
+          <t>71894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>76294</t>
+          <t>86567</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>135096</t>
+          <t>158461</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27993; 51467</t>
+          <t>27527; 49717</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>161717; 199949</t>
+          <t>164607; 198764</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94756; 126422</t>
+          <t>93446; 126802</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45101; 74258</t>
+          <t>56281; 91146</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60920; 89816</t>
+          <t>61893; 91518</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>198212; 238385</t>
+          <t>200824; 237383</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>140709; 179310</t>
+          <t>140306; 179025</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>40801; 105358</t>
+          <t>72756; 101401</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>95502; 132639</t>
+          <t>94285; 132999</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>376949; 426759</t>
+          <t>374793; 428235</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>244170; 295131</t>
+          <t>243846; 295537</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>84956; 165343</t>
+          <t>135145; 181773</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>26399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53417</t>
+          <t>60791</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>30437; 52006</t>
+          <t>30849; 53697</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>80244; 107448</t>
+          <t>78962; 106537</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90781; 114925</t>
+          <t>89918; 115036</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16187; 30471</t>
+          <t>19310; 35745</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32805; 57468</t>
+          <t>34071; 57947</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>98255; 126016</t>
+          <t>98022; 127753</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>107675; 133578</t>
+          <t>107744; 132708</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14205; 45687</t>
+          <t>27948; 43145</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71824; 104050</t>
+          <t>71861; 103671</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>185513; 224796</t>
+          <t>186551; 226169</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>205119; 241267</t>
+          <t>204820; 240396</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>30474; 69126</t>
+          <t>51279; 71442</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57830</t>
+          <t>60259</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>70800</t>
+          <t>72627</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>128630</t>
+          <t>132886</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22952; 43792</t>
+          <t>23066; 43336</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>104617; 136661</t>
+          <t>106123; 138105</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69202; 95112</t>
+          <t>68477; 95801</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46812; 69323</t>
+          <t>51052; 72943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36259; 60656</t>
+          <t>36702; 60606</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>106287; 136967</t>
+          <t>105845; 136328</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>80347; 110412</t>
+          <t>78937; 109794</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>61288; 82190</t>
+          <t>61993; 82729</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64755; 96435</t>
+          <t>64829; 96597</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>219574; 263354</t>
+          <t>221068; 265041</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>158058; 196193</t>
+          <t>154336; 195325</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>113642; 144340</t>
+          <t>118100; 148701</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>48547</t>
+          <t>59456</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>266994</t>
+          <t>82679</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>315542</t>
+          <t>142135</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>71789; 105352</t>
+          <t>70662; 109623</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>227721; 275372</t>
+          <t>227186; 275377</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>136207; 178958</t>
+          <t>137578; 179374</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35503; 65774</t>
+          <t>44771; 76723</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>121428; 159561</t>
+          <t>119039; 160428</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>263708; 314327</t>
+          <t>263599; 312666</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>222283; 271583</t>
+          <t>221984; 270891</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>84561; 493758</t>
+          <t>69162; 98667</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>203307; 258871</t>
+          <t>204436; 256717</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>508508; 577535</t>
+          <t>503226; 570972</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>372323; 437270</t>
+          <t>374750; 440291</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>130415; 676363</t>
+          <t>123394; 166203</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>170592</t>
+          <t>206518</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>255117</t>
+          <t>301683</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>425709</t>
+          <t>508202</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>152931; 199317</t>
+          <t>151849; 196233</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>292053; 342547</t>
+          <t>292553; 343798</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>322634; 370107</t>
+          <t>322913; 370685</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>154359; 191356</t>
+          <t>184722; 229534</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>151235; 197550</t>
+          <t>150501; 195717</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>364172; 420569</t>
+          <t>362795; 418069</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>422707; 477882</t>
+          <t>425472; 479528</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>236019; 274828</t>
+          <t>280688; 326579</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321164; 384120</t>
+          <t>317751; 383960</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>674066; 749433</t>
+          <t>671942; 747811</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>760352; 835157</t>
+          <t>763019; 835449</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>398780; 452542</t>
+          <t>476010; 540199</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>496170</t>
+          <t>571250</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>904961</t>
+          <t>798531</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1401131</t>
+          <t>1369781</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>498664; 585848</t>
+          <t>494437; 581117</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1366860; 1474978</t>
+          <t>1366682; 1477050</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>992738; 1089928</t>
+          <t>989298; 1093685</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>456947; 536612</t>
+          <t>526661; 616392</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>705160; 801015</t>
+          <t>705373; 797847</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1642075; 1759869</t>
+          <t>1646138; 1755358</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1332406; 1446870</t>
+          <t>1329864; 1438320</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>735655; 1404661</t>
+          <t>761055; 840593</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1231143; 1358193</t>
+          <t>1230628; 1358434</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3046118; 3207681</t>
+          <t>3038954; 3202251</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2355148; 2502314</t>
+          <t>2346271; 2495542</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1219515; 1961677</t>
+          <t>1311410; 1430828</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
+          <t>Población que convive con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
